--- a/data/attendance/ANNEX_لعروسي_3AM.xlsx
+++ b/data/attendance/ANNEX_لعروسي_3AM.xlsx
@@ -59,12 +59,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="B11" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5d347aef-5a9a-4422-89df-34f611d9020f</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <t>student_id:87f3130f-93f8-491e-b707-24653dd65149</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>لعروسي 3AM  |  ANNEX  |  3AM  |  لعروسي صاندرا</t>
   </si>
@@ -78,6 +92,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -87,6 +104,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -108,6 +128,12 @@
     <t>عياشي رؤى</t>
   </si>
   <si>
+    <t>قاولي ندى</t>
+  </si>
+  <si>
+    <t>براهيمي محمد رصلان</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -135,7 +161,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -625,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -651,7 +680,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -661,10 +690,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -706,46 +738,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -753,7 +785,7 @@
         <v>501</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -797,7 +829,7 @@
         <v>502</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -841,7 +873,7 @@
         <v>503</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -885,7 +917,7 @@
         <v>504</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -929,7 +961,7 @@
         <v>505</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -973,7 +1005,7 @@
         <v>506</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1009,6 +1041,94 @@
         <v>0</v>
       </c>
       <c r="N10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>910</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>967</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1028,7 +1148,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1036,77 +1156,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
